--- a/metadata/project-metadata.xlsx
+++ b/metadata/project-metadata.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>cc-by-4.0</t>
+          <t>mit</t>
         </is>
       </c>
     </row>

--- a/metadata/project-metadata.xlsx
+++ b/metadata/project-metadata.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mit</t>
+          <t>cc-by-4.0</t>
         </is>
       </c>
     </row>
